--- a/Encollect_Web_DBS_P3/Cypress/fixtures/Bulktrail.xlsx
+++ b/Encollect_Web_DBS_P3/Cypress/fixtures/Bulktrail.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -410,10 +410,10 @@
         <v>RightPartyContact</v>
       </c>
       <c r="D1" t="str">
-        <v>Action Code</v>
+        <v>Disposition Code Group</v>
       </c>
       <c r="E1" t="str">
-        <v>ResultCode</v>
+        <v>Disposition Code</v>
       </c>
       <c r="F1" t="str">
         <v>Next Action Date</v>
@@ -493,7 +493,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Encollect_Web_DBS_P3/Cypress/fixtures/Bulktrail.xlsx
+++ b/Encollect_Web_DBS_P3/Cypress/fixtures/Bulktrail.xlsx
@@ -460,7 +460,7 @@
         <v>PTP</v>
       </c>
       <c r="E2" t="str">
-        <v>BOTP</v>
+        <v>PTP</v>
       </c>
       <c r="F2" t="str">
         <v>2025-06-28</v>
